--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="參數定義" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +28,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +58,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,7 +529,6 @@
           <t>gold</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>50000</v>
       </c>
@@ -553,7 +570,6 @@
           <t>gold</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>100000</v>
       </c>
@@ -582,7 +598,6 @@
           <t>upgradeCount</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>10</v>
       </c>
@@ -591,7 +606,6 @@
           <t>scrap</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>200</v>
       </c>
@@ -620,7 +634,6 @@
           <t>rerollCount</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>2</v>
       </c>
@@ -629,7 +642,6 @@
           <t>essence</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>20</v>
       </c>
@@ -717,7 +729,6 @@
           <t>scrap</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>500</v>
       </c>
@@ -759,7 +770,6 @@
           <t>skillXp</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>10000</v>
       </c>
@@ -768,7 +778,6 @@
           <t>技能經驗值+10000</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -784,7 +793,6 @@
           <t>upgradeCount</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>20</v>
       </c>
@@ -793,7 +801,6 @@
           <t>scrap</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>500</v>
       </c>
@@ -868,7 +875,6 @@
           <t>socketCount</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>8</v>
       </c>
@@ -910,7 +916,6 @@
           <t>enchantCount</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>2</v>
       </c>
@@ -952,7 +957,6 @@
           <t>forgeParts</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>4</v>
       </c>
@@ -961,7 +965,6 @@
           <t>essence</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>50</v>
       </c>
@@ -990,7 +993,6 @@
           <t>composeCount</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>1</v>
       </c>
@@ -1091,7 +1093,6 @@
           <t>scrap</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>500</v>
       </c>
@@ -1120,7 +1121,6 @@
           <t>socketCount</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>16</v>
       </c>
@@ -1175,7 +1175,6 @@
           <t>skillXp</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>50000</v>
       </c>
@@ -1184,7 +1183,6 @@
           <t>技能經驗值+50000</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1200,7 +1198,6 @@
           <t>maxHp</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>5000</v>
       </c>
@@ -1209,7 +1206,6 @@
           <t>gold</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>300000</v>
       </c>
@@ -1218,7 +1214,6 @@
           <t>金幣+300000</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1260,7 +1255,6 @@
           <t>任意2太古史詩50級裝備×1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1289,7 +1283,6 @@
           <t>essence</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>100</v>
       </c>
@@ -1318,7 +1311,6 @@
           <t>ancientCount</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>5</v>
       </c>
@@ -1327,7 +1319,6 @@
           <t>essence</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>300</v>
       </c>
@@ -1382,7 +1373,387 @@
           <t>任意3太古傳說100級裝備×1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>任務表（Task）欄位與參數定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>本頁為說明頁，程式不讀取；第一頁「Task」才是資料來源。改完存檔（Ctrl+S）後雙擊「套用參數.bat」套用，本機開著的遊戲約 2 秒自動重載。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>── 各欄位 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>順序：任務編號（1 起）。玩家依此順序逐一領取，只有當前任務可領。⚠️ 鑰匙欄：請勿變動既有列的順序值，改了會被當成新任務。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>任務說明：遊戲內顯示的任務名稱（戰鬥區快捷列與任務總覽）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>目標類型：進度怎麼計算，見下方「目標類型」清單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>目標參數：搭配目標類型的附加參數；多個值用直線「|」分隔，格式見各類型說明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>目標數量：達成門檻；進度 ≥ 此值即可領取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>獎勵類型：發什麼獎，見下方「獎勵類型」清單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>獎勵參數：搭配獎勵類型的附加參數，格式見各類型說明。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>獎勵數量：發放數量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>獎勵顯示：遊戲內顯示的獎勵文字。⚠️ 程式是照「獎勵類型/參數/數量」發獎，此欄只負責顯示——改數值時記得同步改這裡，否則玩家看到的和實拿的會不一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>備註：純說明欄，給編表的人看，不會進遊戲（也不寫回程式）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>── 目標類型（與目標參數格式） ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>equipSlots＝身上部位數：計算身上滿足條件的部位數（共 13 部位；雙手武器視同佔用主手＋副手兩格）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　目標參數＝最低品質|最低等級。例：0|0＝任意裝備、2|0＝稀有(含)以上、4|50＝史詩(含)以上且裝備等級 50(含)以上。品質索引見下方對照表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>upgradeCount＝累計強化成功次數（失敗不計）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>rerollCount＝累計洗煉次數（整件洗與單條洗各計 1 次）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>enchantCount＝累計附魔成功次數（被拒不計）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>composeCount＝累計寶石合成次數（「全部合成」一次合 N 組計 N）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>socketCount＝身上目前同時鑲嵌的寶石數（拔下即減，重複拔裝不累加）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>forgeParts＝所有熔爐目前已裝配的零件總數（卸下即減）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ancientCount＝身上裝備的太古詞條（帶✡星）總數。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>maxHp＝生命最大值（屬性面板數值；掉回門檻以下進度也會掉）。目標參數留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>stageClear＝通關指定地圖第 N 關（N＝目標數量）。目標參數＝地圖識別碼，見下方對照表。⚠️ 目標關卡請低於該地圖最後一關。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>skillLevel＝指定技能達到 N 級（N＝目標數量；1＝學會）。目標參數＝技能 id（查 Skills 表第一欄）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>── 獎勵類型（與獎勵參數格式） ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>gold＝金幣、scrap＝裝備碎片、essence＝附魔精華：獎勵參數留空；獎勵數量＝發放量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>skillXp＝技能熟練度經驗：獎勵參數留空；獎勵數量＝經驗值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>gem＝寶石（種類隨機）：獎勵參數＝寶石等級 1~5；獎勵數量＝顆數（每顆種類各自隨機）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>book＝附魔書：獎勵參數＝附魔書 id（見下方對照表）；獎勵數量＝本數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>equip＝裝備：獎勵參數＝品質|等級|太古數；獎勵數量＝件數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　品質＝品質索引（見下方對照表）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　等級＝裝備等級；填 0＝依玩家當前關卡自動決定（裝備等級以 50 關為一階：1~49 關為 1 級裝、50~99 關為 50 級裝…）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　太古數＝固定太古詞條條數；整段留空＝依一般掉落規則自然擲骰。例：3|1＝獨特 1 級（太古自然擲骰）、4|50|2＝史詩 50 級固定 2 條太古。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>── 品質索引對照 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>0＝普通、1＝精良、2＝稀有、3＝獨特、4＝史詩、5＝傳說、6＝神話、7＝創世、8＝神鑄創世、9＝混沌、10＝神鑄混沌</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>── 地圖識別碼對照 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>plains＝草原、desert＝荒漠、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>── 附魔書 id 對照 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>fire＝火焰附魔、ice＝冰凍附魔、lightning＝閃電附魔、poison＝毒液附魔、light＝聖光附魔、dark＝暗影附魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>fireRes＝火焰抗性、iceRes＝冰霜抗性、lightningRes＝雷電抗性、poisonRes＝劇毒抗性、lightRes＝聖光抗性、darkRes＝暗影抗性、ctrlRes＝控制抵抗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>loot＝尋寶附魔、haste＝疾行附魔、vigor＝活力附魔、clarity＝澄明附魔、focus＝專注附魔、fortune＝財運附魔、wisdom＝智慧附魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>── 新增／修改任務注意 ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>1. 任務嚴格照「順序」逐一領取；新增任務請接在最後一列、給新的順序值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2. 玩家存檔只記「已領到第幾個」，刪除或重排既有任務會讓舊玩家的進度指到錯的任務；上線後請避免刪列與重排，要停用就把該任務改成極易達成的內容。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>3. 累計型（強化/洗煉/附魔/合成）跨任務共用同一個計數：例「強化10次」與「強化20次」共用，前者完成時後者即為 10/20。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>4. 品質/等級門檻是「以上皆可」：稀有任務穿史詩也算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>5. 改完別忘了同步「獎勵顯示」欄的文字。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EADCFD9-0E24-4643-8149-D4E70F21229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D0D9F7-9B54-47EE-ABF1-F4C8544A8A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" r:id="rId1"/>
     <sheet name="參數定義" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="181">
   <si>
     <t>順序</t>
   </si>
@@ -113,9 +126,6 @@
     <t>累計洗煉次數（整件或單條皆計1次）</t>
   </si>
   <si>
-    <t>挑戰草原第20關成功</t>
-  </si>
-  <si>
     <t>stageClear</t>
   </si>
   <si>
@@ -131,9 +141,6 @@
     <t>任意獨特1級裝備×1</t>
   </si>
   <si>
-    <t>通關草原地圖第20關</t>
-  </si>
-  <si>
     <t>將全身的裝備替換成獨特品質</t>
   </si>
   <si>
@@ -164,9 +171,6 @@
     <t>強化裝備20次</t>
   </si>
   <si>
-    <t>挑戰草原第30關成功</t>
-  </si>
-  <si>
     <t>獎勵裝備等級依當前關卡</t>
   </si>
   <si>
@@ -224,18 +228,12 @@
     <t>累計合成次數</t>
   </si>
   <si>
-    <t>挑戰草原第40關成功</t>
-  </si>
-  <si>
     <t>4|1|2</t>
   </si>
   <si>
     <t>任意2太古史詩1級裝備×1</t>
   </si>
   <si>
-    <t>通關草原地圖第40關</t>
-  </si>
-  <si>
     <t>穿上4件史詩裝備</t>
   </si>
   <si>
@@ -272,9 +270,6 @@
     <t>金幣+300000</t>
   </si>
   <si>
-    <t>挑戰草原第50關BOSS成功</t>
-  </si>
-  <si>
     <t>4|50|2</t>
   </si>
   <si>
@@ -302,9 +297,6 @@
     <t>全身裝備加總的太古詞條(帶星)數</t>
   </si>
   <si>
-    <t>挑戰草原第100關BOSS成功</t>
-  </si>
-  <si>
     <t>5|100|3</t>
   </si>
   <si>
@@ -383,9 +375,6 @@
     <t>maxHp＝生命最大值（屬性面板數值；掉回門檻以下進度也會掉）。目標參數留空。</t>
   </si>
   <si>
-    <t>stageClear＝通關指定地圖第 N 關（N＝目標數量）。目標參數＝地圖識別碼，見下方對照表。⚠️ 目標關卡請低於該地圖最後一關。</t>
-  </si>
-  <si>
     <t>skillLevel＝指定技能達到 N 級（N＝目標數量；1＝學會）。目標參數＝技能 id（查 Skills 表第一欄）。</t>
   </si>
   <si>
@@ -478,13 +467,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>挑戰草原第150關BOSS成功</t>
-  </si>
-  <si>
-    <t>挑戰草原第150關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>任意3太古傳說150級裝備×1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -528,10 +510,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>挑戰草原第200關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>任意3太古傳說200級裝備×1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -540,42 +518,89 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>新增說明</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>towerFloor</t>
+  </si>
+  <si>
+    <t>forgePartLevel</t>
+  </si>
+  <si>
+    <t>desert</t>
+  </si>
+  <si>
+    <t>forgePartLevel＝目前等級最高的熔爐零件是幾級（任一種零件達 N 級即可；零件等級是全域的，卸下不影響）。目標參數留空。</t>
+  </si>
+  <si>
+    <t>stageClear＝通關指定地圖第 N 關（N＝目標數量）。目標參數＝地圖識別碼，見下方對照表。可以指定該地圖的最後一關。</t>
+  </si>
+  <si>
+    <t>towerFloor＝高塔已通關的最高層數（N＝目標數量）。目標參數留空；層數與塔別無關（試煉/地獄/煉獄同一條層數軸）。</t>
+  </si>
+  <si>
+    <t>Icefield</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第20關成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第30關成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第40關成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第50關BOSS成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第100關BOSS成功</t>
+  </si>
+  <si>
+    <t>挑戰荒漠第150關BOSS成功</t>
+  </si>
+  <si>
     <t>挑戰荒漠第200關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>任意4太古傳說200級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>5|200|4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增說明</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">towerFloor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forgePartLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forgePartLevel＝目前等級最高的熔爐零件是幾級（任一種零件達 N 級即可；零件等級是全域的，卸下不影響）。目標參數留空。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stageClear＝通關指定地圖第 N 關（N＝目標數量）。目標參數＝地圖識別碼，見下方對照表。可以指定該地圖的最後一關。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">towerFloor＝高塔已通關的最高層數（N＝目標數量）。目標參數留空；層數與塔別無關（試煉/地獄/煉獄同一條層數軸）。</t>
+  </si>
+  <si>
+    <t>通關荒漠地圖第20關</t>
+  </si>
+  <si>
+    <t>通關荒漠地圖第40關</t>
+  </si>
+  <si>
+    <t>swamp</t>
+  </si>
+  <si>
+    <t>挑戰冰原第400關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰冰原第300關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5|300|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|400|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古傳說300級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4神話傳說400級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">挑戰沼澤第400關BOSS成功</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desert＝荒漠、Icefield＝冰原、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
   </si>
 </sst>
 </file>
@@ -594,16 +619,22 @@
       <b/>
       <sz val="11"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="9"/>
@@ -955,8 +986,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -967,7 +998,7 @@
     <col min="10" max="10" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -999,10 +1030,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1031,7 +1062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1060,7 +1091,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1086,7 +1117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1112,50 +1143,50 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E6">
         <v>20</v>
       </c>
       <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>13</v>
@@ -1167,44 +1198,44 @@
         <v>500</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8">
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -1219,59 +1250,59 @@
         <v>500</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1280,50 +1311,50 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1335,27 +1366,27 @@
         <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1364,56 +1395,56 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -1425,27 +1456,27 @@
         <v>500</v>
       </c>
       <c r="I16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1454,47 +1485,47 @@
         <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H18">
         <v>50000</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E19">
         <v>5000</v>
@@ -1506,50 +1537,50 @@
         <v>300000</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>13</v>
@@ -1561,21 +1592,21 @@
         <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -1587,47 +1618,47 @@
         <v>200</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="J22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -1642,59 +1673,59 @@
         <v>300</v>
       </c>
       <c r="I24" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="J25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1703,24 +1734,21 @@
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>162</v>
-      </c>
-      <c r="K26" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E27">
         <v>13</v>
@@ -1732,18 +1760,18 @@
         <v>50000</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="J27" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
@@ -1758,21 +1786,21 @@
         <v>300</v>
       </c>
       <c r="I28" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1784,80 +1812,97 @@
         <v>2000000</v>
       </c>
       <c r="I29" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J29" t="s">
-        <v>159</v>
-      </c>
-      <c r="K29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>164</v>
-      </c>
-      <c r="J30" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E31">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>167</v>
-      </c>
-      <c r="J31" t="s">
-        <v>166</v>
-      </c>
-      <c r="K31" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32">
+        <v>400</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1869,285 +1914,285 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-    </row>
-    <row r="32" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
-    </row>
-    <row r="45" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
-    </row>
-    <row r="48" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D0D9F7-9B54-47EE-ABF1-F4C8544A8A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03088D3-4B31-47CE-B727-A7E8C716D369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="194">
   <si>
     <t>順序</t>
   </si>
@@ -129,9 +129,6 @@
     <t>stageClear</t>
   </si>
   <si>
-    <t>plains</t>
-  </si>
-  <si>
     <t>equip</t>
   </si>
   <si>
@@ -414,9 +411,6 @@
     <t>── 地圖識別碼對照 ──</t>
   </si>
   <si>
-    <t>plains＝草原、desert＝荒漠、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
-  </si>
-  <si>
     <t>── 附魔書 id 對照 ──</t>
   </si>
   <si>
@@ -573,10 +567,6 @@
     <t>swamp</t>
   </si>
   <si>
-    <t>挑戰冰原第400關BOSS成功</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>挑戰冰原第300關BOSS成功</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -593,14 +583,77 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>任意4神話傳說400級裝備×1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">挑戰沼澤第400關BOSS成功</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desert＝荒漠、Icefield＝冰原、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
+    <t>挑戰沼澤第400關BOSS成功</t>
+  </si>
+  <si>
+    <t>desert＝荒漠、Icefield＝冰原、swamp＝沼澤、undead_mountains＝亡靈山脈、god_battlefield＝太古戰場、god_chaos＝混沌界、god_sanctuary＝永恒神域</t>
+  </si>
+  <si>
+    <t>升級熔爐任意零件至4級</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金幣+3000000</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰冰原第250關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰沼澤第350關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>swamp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>undead_mountains</t>
+  </si>
+  <si>
+    <t>7|450|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古神話400級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古創世450級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古創世500級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>7|500|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古傳說250級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5|250|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6|350|4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意4太古神話350級裝備×1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰亡靈山脈第450關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>挑戰亡靈山脈第500關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -986,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1030,7 +1083,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1148,31 +1201,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>20</v>
       </c>
       <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>33</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1180,13 +1233,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>13</v>
@@ -1198,10 +1251,10 @@
         <v>500</v>
       </c>
       <c r="I7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" t="s">
         <v>37</v>
-      </c>
-      <c r="J7" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1209,25 +1262,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8">
         <v>10000</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1235,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
@@ -1250,7 +1303,7 @@
         <v>500</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" t="s">
         <v>24</v>
@@ -1261,31 +1314,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E10">
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1293,16 +1346,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
         <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1311,10 +1364,10 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" t="s">
         <v>49</v>
-      </c>
-      <c r="J11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1322,28 +1375,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
         <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
         <v>53</v>
-      </c>
-      <c r="G12" t="s">
-        <v>54</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" t="s">
         <v>55</v>
-      </c>
-      <c r="J12" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1351,10 +1404,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1366,10 +1419,10 @@
         <v>50</v>
       </c>
       <c r="I13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" t="s">
         <v>59</v>
-      </c>
-      <c r="J13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1377,16 +1430,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
         <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1395,10 +1448,10 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1406,31 +1459,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15">
         <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1438,13 +1491,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -1456,10 +1509,10 @@
         <v>500</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1467,16 +1520,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1485,10 +1538,10 @@
         <v>15</v>
       </c>
       <c r="I17" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" t="s">
         <v>70</v>
-      </c>
-      <c r="J17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1496,25 +1549,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
         <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H18">
         <v>50000</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1522,10 +1575,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
         <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
       </c>
       <c r="E19">
         <v>5000</v>
@@ -1537,7 +1590,7 @@
         <v>300000</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1545,28 +1598,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>50</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1574,13 +1627,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>13</v>
@@ -1592,10 +1645,10 @@
         <v>100</v>
       </c>
       <c r="I21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" t="s">
         <v>82</v>
-      </c>
-      <c r="J21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1603,10 +1656,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
         <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -1618,10 +1671,10 @@
         <v>200</v>
       </c>
       <c r="I22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1629,28 +1682,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E23">
         <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1658,7 +1711,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
@@ -1673,7 +1726,7 @@
         <v>300</v>
       </c>
       <c r="I24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
@@ -1684,31 +1737,31 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E25">
         <v>150</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1716,16 +1769,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1734,7 +1787,7 @@
         <v>15</v>
       </c>
       <c r="I26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1742,13 +1795,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E27">
         <v>13</v>
@@ -1760,10 +1813,10 @@
         <v>50000</v>
       </c>
       <c r="I27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1771,7 +1824,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
@@ -1786,7 +1839,7 @@
         <v>300</v>
       </c>
       <c r="I28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J28" t="s">
         <v>29</v>
@@ -1797,10 +1850,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1812,10 +1865,10 @@
         <v>2000000</v>
       </c>
       <c r="I29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J29" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1823,28 +1876,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1852,27 +1905,24 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E31">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2000000</v>
       </c>
       <c r="I31" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31" t="s">
         <v>177</v>
       </c>
     </row>
@@ -1887,22 +1937,167 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E32">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33">
+        <v>300</v>
+      </c>
+      <c r="F33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" t="s">
+        <v>172</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34">
+        <v>350</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35">
+        <v>400</v>
+      </c>
+      <c r="F35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" t="s">
+        <v>173</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36">
+        <v>450</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37">
+        <v>500</v>
+      </c>
+      <c r="F37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1921,12 +2116,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -1934,57 +2129,57 @@
     </row>
     <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -1992,77 +2187,77 @@
     </row>
     <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
@@ -2070,47 +2265,47 @@
     </row>
     <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
@@ -2118,12 +2313,12 @@
     </row>
     <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
@@ -2131,12 +2326,12 @@
     </row>
     <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -2144,22 +2339,22 @@
     </row>
     <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -2167,32 +2362,32 @@
     </row>
     <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Task.xlsx
+++ b/config/Excel/Task.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03088D3-4B31-47CE-B727-A7E8C716D369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7805C9A5-DF28-4760-9993-F02F11679688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="207">
   <si>
     <t>順序</t>
   </si>
@@ -216,9 +216,6 @@
     <t>檢查熔爐目前已裝配的零件總數</t>
   </si>
   <si>
-    <t>合成寶石1次</t>
-  </si>
-  <si>
     <t>composeCount</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
     <t>任意2太古史詩50級裝備×1</t>
   </si>
   <si>
-    <t>將全身的裝備替換成50級史詩品質</t>
-  </si>
-  <si>
     <t>4|50</t>
   </si>
   <si>
@@ -294,12 +288,6 @@
     <t>全身裝備加總的太古詞條(帶星)數</t>
   </si>
   <si>
-    <t>5|100|3</t>
-  </si>
-  <si>
-    <t>任意3太古傳說100級裝備×1</t>
-  </si>
-  <si>
     <t>任務表（Task）欄位與參數定義</t>
   </si>
   <si>
@@ -653,6 +641,74 @@
   </si>
   <si>
     <t>挑戰亡靈山脈第500關BOSS成功</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將4件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將8件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將13件裝備替換成50級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>附魔精華+400</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化裝備30次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備碎片+500</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化裝備40次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備鑲嵌任意寶石10顆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意1級寶石×40</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將4件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將8件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>將13件裝備替換成100級史詩品質</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4|100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備鑲嵌任意寶石20顆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成寶石2次</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4|100|3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>任意3太古史詩100級裝備×1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1039,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1083,7 +1139,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1201,13 +1257,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E6">
         <v>20</v>
@@ -1225,7 +1281,7 @@
         <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1314,13 +1370,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -1329,13 +1385,13 @@
         <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J10" t="s">
         <v>44</v>
@@ -1430,13 +1486,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
         <v>47</v>
@@ -1451,7 +1507,7 @@
         <v>48</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1459,13 +1515,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C15" t="s">
         <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E15">
         <v>40</v>
@@ -1474,16 +1530,16 @@
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1491,13 +1547,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -1512,7 +1568,7 @@
         <v>36</v>
       </c>
       <c r="J16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1520,7 +1576,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
         <v>46</v>
@@ -1538,10 +1594,10 @@
         <v>15</v>
       </c>
       <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" t="s">
         <v>69</v>
-      </c>
-      <c r="J17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1549,13 +1605,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
         <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -1567,7 +1623,7 @@
         <v>50000</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1575,10 +1631,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
         <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
       </c>
       <c r="E19">
         <v>5000</v>
@@ -1590,7 +1646,7 @@
         <v>300000</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1598,13 +1654,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
         <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E20">
         <v>50</v>
@@ -1613,13 +1669,13 @@
         <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1627,16 +1683,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -1645,10 +1701,10 @@
         <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1656,25 +1712,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H22">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I22" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1682,28 +1738,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>134</v>
+      </c>
+      <c r="J23" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1711,22 +1767,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="C24" t="s">
         <v>21</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H24">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I24" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="J24" t="s">
         <v>24</v>
@@ -1737,31 +1793,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="E25">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I25" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="J25" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1769,25 +1822,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="C26" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H26">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="I26" t="s">
-        <v>150</v>
+        <v>195</v>
+      </c>
+      <c r="J26" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1795,28 +1848,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="E27">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>47</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>50000</v>
+        <v>40</v>
       </c>
       <c r="I27" t="s">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="J27" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1824,25 +1877,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
         <v>27</v>
       </c>
       <c r="H28">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I28" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J28" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1850,254 +1903,616 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>155</v>
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="G29" t="s">
+        <v>205</v>
       </c>
       <c r="H29">
-        <v>2000000</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>149</v>
-      </c>
-      <c r="J29" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="E30">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>79</v>
+      </c>
+      <c r="J30" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H31">
-        <v>2000000</v>
+        <v>500</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="J31" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32">
+        <v>200</v>
+      </c>
+      <c r="I32" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33">
+        <v>500</v>
+      </c>
+      <c r="I33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34">
+        <v>13</v>
+      </c>
+      <c r="F34" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34">
+        <v>400</v>
+      </c>
+      <c r="I34" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35">
+        <v>500</v>
+      </c>
+      <c r="I35" t="s">
+        <v>195</v>
+      </c>
+      <c r="J35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>40</v>
+      </c>
+      <c r="I36" t="s">
+        <v>198</v>
+      </c>
+      <c r="J36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H37">
+        <v>300</v>
+      </c>
+      <c r="I37" t="s">
+        <v>135</v>
+      </c>
+      <c r="J37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="G38" t="s">
+        <v>137</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>136</v>
+      </c>
+      <c r="J38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E39">
+        <v>5</v>
+      </c>
+      <c r="F39" t="s">
+        <v>47</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40">
+        <v>50000</v>
+      </c>
+      <c r="I40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>31</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H41">
+        <v>300</v>
+      </c>
+      <c r="I41" t="s">
+        <v>135</v>
+      </c>
+      <c r="J41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42">
+        <v>2000000</v>
+      </c>
+      <c r="I42" t="s">
+        <v>145</v>
+      </c>
+      <c r="J42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>33</v>
+      </c>
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43">
+        <v>200</v>
+      </c>
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>2000000</v>
+      </c>
+      <c r="I44" t="s">
+        <v>174</v>
+      </c>
+      <c r="J44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45">
+        <v>250</v>
+      </c>
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" t="s">
+        <v>185</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" t="s">
+        <v>156</v>
+      </c>
+      <c r="E46">
+        <v>300</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>37</v>
+      </c>
+      <c r="B47" t="s">
+        <v>176</v>
+      </c>
+      <c r="C47" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" t="s">
+        <v>166</v>
+      </c>
+      <c r="E47">
+        <v>350</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="s">
+        <v>186</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48">
+        <v>400</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>169</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49">
+        <v>450</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
         <v>179</v>
       </c>
-      <c r="C32" t="s">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C50" t="s">
         <v>30</v>
       </c>
-      <c r="D32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32">
-        <v>250</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="D50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50">
+        <v>500</v>
+      </c>
+      <c r="F50" t="s">
         <v>31</v>
       </c>
-      <c r="G32" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32">
+      <c r="G50" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50">
         <v>1</v>
       </c>
-      <c r="I32" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>171</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33">
-        <v>300</v>
-      </c>
-      <c r="F33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" t="s">
-        <v>172</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34">
-        <v>350</v>
-      </c>
-      <c r="F34" t="s">
-        <v>31</v>
-      </c>
-      <c r="G34" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" t="s">
-        <v>181</v>
-      </c>
-      <c r="E35">
-        <v>400</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G35" t="s">
-        <v>173</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>192</v>
-      </c>
-      <c r="C36" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="I50" t="s">
         <v>182</v>
-      </c>
-      <c r="E36">
-        <v>450</v>
-      </c>
-      <c r="F36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>193</v>
-      </c>
-      <c r="C37" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E37">
-        <v>500</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" t="s">
-        <v>187</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2116,12 +2531,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -2129,57 +2544,57 @@
     </row>
     <row r="4" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -2187,77 +2602,77 @@
     </row>
     <row r="16" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
@@ -2265,47 +2680,47 @@
     </row>
     <row r="32" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
@@ -2313,12 +2728,12 @@
     </row>
     <row r="42" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
@@ -2326,12 +2741,12 @@
     </row>
     <row r="45" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
@@ -2339,22 +2754,22 @@
     </row>
     <row r="48" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
@@ -2362,32 +2777,32 @@
     </row>
     <row r="53" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
